--- a/survey_templates/038_dental_arcade_morphogenesis_survey--survey_templates.xlsx
+++ b/survey_templates/038_dental_arcade_morphogenesis_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Page 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Page 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email Page 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone Page 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -960,12 +960,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -993,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1027,46 +1027,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>demographics_page_choices</t>
+          <t>questions_page_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>demographics_page_choices</t>
+          <t>questions_page_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1078,46 +1078,46 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>questions_page_choices</t>
+          <t>assessment_page_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>questions_page_choices</t>
+          <t>assessment_page_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1129,46 +1129,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>assessment_page_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>assessment_page_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
